--- a/sheets/민요/검수/창부타령 1.xlsx
+++ b/sheets/민요/검수/창부타령 1.xlsx
@@ -413,7 +413,7 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">― 연음 · △ 쉼 · 점 · ○ 동그라미 · ⁚ 두 점 · ‹ 정간 경계 표시 · ／ 사선 (· ○ ⁚ ‹ ／ 는 화면 표시 전용)</t>
+          <t xml:space="preserve">– 연음 · △ 쉼 · 점 · ○ 동그라미 · ⁚ 두 점 · ‹ 정간 경계 표시 · ／ 사선 (· ○ ⁚ ‹ ／ 는 화면 표시 전용)</t>
         </is>
       </c>
     </row>
@@ -597,12 +597,12 @@
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I3" s="2"/>
@@ -632,12 +632,12 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -706,12 +706,12 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I6" s="2"/>
@@ -741,12 +741,12 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―|△</t>
+          <t xml:space="preserve">–|△</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 △</t>
         </is>
       </c>
@@ -1087,13 +1087,13 @@
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">姑|―</t>
+          <t xml:space="preserve">姑|–</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
-―</t>
+–</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1250,12 +1250,12 @@
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1324,12 +1324,12 @@
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I22" s="2"/>
@@ -1359,12 +1359,12 @@
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―|△</t>
+          <t xml:space="preserve">–|△</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 △</t>
         </is>
       </c>
@@ -1754,12 +1754,12 @@
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―|姑</t>
+          <t xml:space="preserve">–|姑</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 姑</t>
         </is>
       </c>
@@ -1874,12 +1874,12 @@
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I36" s="2"/>
@@ -2192,12 +2192,12 @@
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I44" s="2"/>
@@ -2456,12 +2456,12 @@
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I51" s="2"/>
@@ -2491,13 +2491,13 @@
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰|―</t>
+          <t xml:space="preserve">汰|–</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">汰
-―</t>
+–</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
@@ -2865,13 +2865,13 @@
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰|―</t>
+          <t xml:space="preserve">汰|–</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">汰
-―</t>
+–</t>
         </is>
       </c>
       <c r="I62" s="2" t="inlineStr">
@@ -2979,12 +2979,12 @@
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―|姑</t>
+          <t xml:space="preserve">–|姑</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 姑</t>
         </is>
       </c>
@@ -3099,12 +3099,12 @@
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I68" s="2" t="inlineStr">
@@ -3740,12 +3740,12 @@
       </c>
       <c r="G84" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H84" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I84" s="2" t="inlineStr">
@@ -4249,12 +4249,12 @@
       </c>
       <c r="G97" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">―|姑</t>
+          <t xml:space="preserve">–|姑</t>
         </is>
       </c>
       <c r="H97" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 姑</t>
         </is>
       </c>
@@ -4421,12 +4421,12 @@
       </c>
       <c r="G101" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H101" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I101" s="2"/>
@@ -4739,12 +4739,12 @@
       </c>
       <c r="G109" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―|無</t>
+          <t xml:space="preserve">–|無</t>
         </is>
       </c>
       <c r="H109" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 無</t>
         </is>
       </c>
@@ -5015,12 +5015,12 @@
       </c>
       <c r="G116" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H116" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I116" s="2" t="inlineStr">
@@ -5361,12 +5361,12 @@
       </c>
       <c r="G125" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―|姑</t>
+          <t xml:space="preserve">–|姑</t>
         </is>
       </c>
       <c r="H125" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 姑</t>
         </is>
       </c>
@@ -5720,7 +5720,7 @@
       </c>
       <c r="J4" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="K4" s="9"/>
@@ -5749,7 +5749,7 @@
       </c>
       <c r="P4" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="Q4" s="9"/>
@@ -5758,7 +5758,7 @@
       <c r="A5" s="0"/>
       <c r="B5" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="C5" s="9" t="inlineStr">
@@ -5779,7 +5779,7 @@
       </c>
       <c r="F5" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="G5" s="9" t="inlineStr">
@@ -5789,7 +5789,7 @@
       </c>
       <c r="H5" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I5" s="9" t="inlineStr">
@@ -5800,7 +5800,7 @@
       <c r="J5" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">汰
-―</t>
+–</t>
         </is>
       </c>
       <c r="K5" s="9" t="inlineStr">
@@ -5810,13 +5810,13 @@
       </c>
       <c r="L5" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="M5" s="9"/>
       <c r="N5" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="O5" s="9" t="inlineStr">
@@ -5826,7 +5826,7 @@
       </c>
       <c r="P5" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="Q5" s="9" t="inlineStr">
@@ -5845,7 +5845,7 @@
       <c r="C6" s="10"/>
       <c r="D6" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="E6" s="10"/>
@@ -5961,13 +5961,13 @@
       </c>
       <c r="N7" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="O7" s="8"/>
       <c r="P7" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="Q7" s="8"/>
@@ -6024,14 +6024,14 @@
       <c r="M8" s="9"/>
       <c r="N8" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 △</t>
         </is>
       </c>
       <c r="O8" s="9"/>
       <c r="P8" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 △</t>
         </is>
       </c>
@@ -6395,7 +6395,7 @@
       </c>
       <c r="L13" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="M13" s="9"/>
@@ -6426,14 +6426,14 @@
       <c r="A14" s="0"/>
       <c r="B14" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 姑</t>
         </is>
       </c>
       <c r="C14" s="10"/>
       <c r="D14" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 無</t>
         </is>
       </c>
@@ -6545,7 +6545,7 @@
       <c r="J15" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">汰
-―</t>
+–</t>
         </is>
       </c>
       <c r="K15" s="8" t="inlineStr">
@@ -6722,7 +6722,7 @@
       <c r="P17" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
-―</t>
+–</t>
         </is>
       </c>
       <c r="Q17" s="9" t="inlineStr">
@@ -6756,7 +6756,7 @@
       </c>
       <c r="F18" s="18" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 姑</t>
         </is>
       </c>
@@ -6777,7 +6777,7 @@
       </c>
       <c r="J18" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 姑</t>
         </is>
       </c>
@@ -6791,7 +6791,7 @@
       <c r="M18" s="13"/>
       <c r="N18" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 姑</t>
         </is>
       </c>

--- a/sheets/민요/검수/창부타령 1.xlsx
+++ b/sheets/민요/검수/창부타령 1.xlsx
@@ -11,27 +11,43 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="4">
+  <fonts count="7">
     <font>
       <sz val="11"/>
-      <name val="맑은 고딕"/>
+      <name val="궁서체"/>
       <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
-      <name val="맑은 고딕"/>
+      <name val="궁서체"/>
       <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="14"/>
-      <name val="맑은 고딕"/>
+      <name val="궁서체"/>
       <family val="2"/>
     </font>
     <font>
       <sz val="22"/>
-      <name val="맑은 고딕"/>
+      <name val="궁서체"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="24"/>
+      <name val="궁서체"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="24"/>
+      <name val="궁서체"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <name val="궁서체"/>
       <family val="2"/>
     </font>
   </fonts>
@@ -134,7 +150,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -157,7 +173,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <!-- 8~16: 박 묶음 가사 칸 = (일반 8~10 · 비고 11~13 · 팔레트 외 14~16) × (첫 · 가운데 · 마지막) -->
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -185,7 +200,6 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <!-- 17~19: 악보 율명 칸 22pt (가사 11pt 의 두 배) = 일반 · 비고 · 팔레트 외 -->
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -193,6 +207,33 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -5568,111 +5609,111 @@
     </row>
     <row r="2" ht="60" customHeight="1">
       <c r="A2" s="0"/>
-      <c r="B2" s="7" t="inlineStr">
+      <c r="B2" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">창부타령 1</t>
         </is>
       </c>
-      <c r="C2" s="7"/>
-      <c r="D2" s="7"/>
-      <c r="E2" s="7"/>
-      <c r="F2" s="7"/>
-      <c r="G2" s="7"/>
-      <c r="H2" s="7"/>
-      <c r="I2" s="7"/>
-      <c r="J2" s="7"/>
-      <c r="K2" s="7"/>
-      <c r="L2" s="7"/>
-      <c r="M2" s="7"/>
-      <c r="N2" s="7"/>
-      <c r="O2" s="7"/>
-      <c r="P2" s="7"/>
-      <c r="Q2" s="7"/>
+      <c r="C2" s="20"/>
+      <c r="D2" s="20"/>
+      <c r="E2" s="20"/>
+      <c r="F2" s="20"/>
+      <c r="G2" s="20"/>
+      <c r="H2" s="20"/>
+      <c r="I2" s="20"/>
+      <c r="J2" s="20"/>
+      <c r="K2" s="20"/>
+      <c r="L2" s="20"/>
+      <c r="M2" s="20"/>
+      <c r="N2" s="20"/>
+      <c r="O2" s="20"/>
+      <c r="P2" s="20"/>
+      <c r="Q2" s="20"/>
     </row>
     <row r="3" ht="56" customHeight="1">
       <c r="A3" s="0"/>
-      <c r="B3" s="18" t="inlineStr">
+      <c r="B3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
 姑</t>
         </is>
       </c>
-      <c r="C3" s="11" t="inlineStr">
+      <c r="C3" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">백</t>
         </is>
       </c>
-      <c r="D3" s="18" t="inlineStr">
+      <c r="D3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">△
 潢</t>
         </is>
       </c>
-      <c r="E3" s="11" t="inlineStr">
+      <c r="E3" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">얼</t>
         </is>
       </c>
-      <c r="F3" s="18" t="inlineStr">
+      <c r="F3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 黃</t>
         </is>
       </c>
-      <c r="G3" s="11" t="inlineStr">
+      <c r="G3" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">이</t>
         </is>
       </c>
-      <c r="H3" s="18" t="inlineStr">
+      <c r="H3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 黃</t>
         </is>
       </c>
-      <c r="I3" s="11" t="inlineStr">
+      <c r="I3" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">일</t>
         </is>
       </c>
-      <c r="J3" s="18" t="inlineStr">
+      <c r="J3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">汰汰</t>
         </is>
       </c>
-      <c r="K3" s="11" t="inlineStr">
+      <c r="K3" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">새</t>
         </is>
       </c>
-      <c r="L3" s="17" t="inlineStr">
+      <c r="L3" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">△</t>
         </is>
       </c>
-      <c r="M3" s="8" t="inlineStr">
+      <c r="M3" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">하</t>
         </is>
       </c>
-      <c r="N3" s="18" t="inlineStr">
+      <c r="N3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 姑</t>
         </is>
       </c>
-      <c r="O3" s="11" t="inlineStr">
+      <c r="O3" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">우</t>
         </is>
       </c>
-      <c r="P3" s="18" t="inlineStr">
+      <c r="P3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 姑</t>
         </is>
       </c>
-      <c r="Q3" s="11" t="inlineStr">
+      <c r="Q3" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">아</t>
         </is>
@@ -5680,156 +5721,156 @@
     </row>
     <row r="4" ht="56" customHeight="1">
       <c r="A4" s="0"/>
-      <c r="B4" s="18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="C4" s="12"/>
-      <c r="D4" s="18" t="inlineStr">
+      <c r="B4" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="C4" s="25"/>
+      <c r="D4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
 㳞</t>
         </is>
       </c>
-      <c r="E4" s="12" t="inlineStr">
+      <c r="E4" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">씨</t>
         </is>
       </c>
-      <c r="F4" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="G4" s="9" t="inlineStr">
+      <c r="F4" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="G4" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">까</t>
         </is>
       </c>
-      <c r="H4" s="17" t="inlineStr">
+      <c r="H4" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 姑</t>
         </is>
       </c>
-      <c r="I4" s="9" t="inlineStr">
+      <c r="I4" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">구</t>
         </is>
       </c>
-      <c r="J4" s="17" t="inlineStr">
+      <c r="J4" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="K4" s="9"/>
-      <c r="L4" s="18" t="inlineStr">
+      <c r="K4" s="26"/>
+      <c r="L4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 潢
 汰</t>
         </is>
       </c>
-      <c r="M4" s="12" t="inlineStr">
+      <c r="M4" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">아</t>
         </is>
       </c>
-      <c r="N4" s="17" t="inlineStr">
+      <c r="N4" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 姑</t>
         </is>
       </c>
-      <c r="O4" s="9" t="inlineStr">
+      <c r="O4" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">련</t>
         </is>
       </c>
-      <c r="P4" s="17" t="inlineStr">
+      <c r="P4" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="Q4" s="9"/>
+      <c r="Q4" s="26"/>
     </row>
     <row r="5" ht="56" customHeight="1">
       <c r="A5" s="0"/>
-      <c r="B5" s="17" t="inlineStr">
+      <c r="B5" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="C5" s="9" t="inlineStr">
+      <c r="C5" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">구</t>
         </is>
       </c>
-      <c r="D5" s="17" t="inlineStr">
+      <c r="D5" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
 仲</t>
         </is>
       </c>
-      <c r="E5" s="9" t="inlineStr">
+      <c r="E5" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">구</t>
         </is>
       </c>
-      <c r="F5" s="17" t="inlineStr">
+      <c r="F5" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="G5" s="9" t="inlineStr">
+      <c r="G5" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">지</t>
         </is>
       </c>
-      <c r="H5" s="17" t="inlineStr">
+      <c r="H5" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="I5" s="9" t="inlineStr">
+      <c r="I5" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">에</t>
         </is>
       </c>
-      <c r="J5" s="17" t="inlineStr">
+      <c r="J5" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">汰
 –</t>
         </is>
       </c>
-      <c r="K5" s="9" t="inlineStr">
+      <c r="K5" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">람</t>
         </is>
       </c>
-      <c r="L5" s="17" t="inlineStr">
+      <c r="L5" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="M5" s="9"/>
-      <c r="N5" s="17" t="inlineStr">
+      <c r="M5" s="26"/>
+      <c r="N5" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="O5" s="9" t="inlineStr">
+      <c r="O5" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">이</t>
         </is>
       </c>
-      <c r="P5" s="17" t="inlineStr">
+      <c r="P5" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="Q5" s="9" t="inlineStr">
+      <c r="Q5" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">니</t>
         </is>
@@ -5837,442 +5878,442 @@
     </row>
     <row r="6" ht="56" customHeight="1">
       <c r="A6" s="0"/>
-      <c r="B6" s="17" t="inlineStr">
+      <c r="B6" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="C6" s="10"/>
-      <c r="D6" s="17" t="inlineStr">
+      <c r="C6" s="27"/>
+      <c r="D6" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="E6" s="10"/>
-      <c r="F6" s="17" t="inlineStr">
+      <c r="E6" s="27"/>
+      <c r="F6" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="G6" s="10"/>
-      <c r="H6" s="17" t="inlineStr">
+      <c r="G6" s="27"/>
+      <c r="H6" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="I6" s="10"/>
-      <c r="J6" s="17" t="inlineStr">
+      <c r="I6" s="27"/>
+      <c r="J6" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">△</t>
         </is>
       </c>
-      <c r="K6" s="10"/>
-      <c r="L6" s="18" t="inlineStr">
+      <c r="K6" s="27"/>
+      <c r="L6" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞
 姑</t>
         </is>
       </c>
-      <c r="M6" s="13" t="inlineStr">
+      <c r="M6" s="28" t="inlineStr">
         <is>
           <t xml:space="preserve">구</t>
         </is>
       </c>
-      <c r="N6" s="17" t="inlineStr">
+      <c r="N6" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="O6" s="10"/>
-      <c r="P6" s="17" t="inlineStr">
+      <c r="O6" s="27"/>
+      <c r="P6" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="Q6" s="10"/>
+      <c r="Q6" s="27"/>
     </row>
     <row r="7" ht="56" customHeight="1">
       <c r="A7" s="0"/>
-      <c r="B7" s="17" t="inlineStr">
+      <c r="B7" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 姑</t>
         </is>
       </c>
-      <c r="C7" s="8" t="inlineStr">
+      <c r="C7" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">야</t>
         </is>
       </c>
-      <c r="D7" s="18" t="inlineStr">
+      <c r="D7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞
 潢</t>
         </is>
       </c>
-      <c r="E7" s="11" t="inlineStr">
+      <c r="E7" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">절</t>
         </is>
       </c>
-      <c r="F7" s="18" t="inlineStr">
+      <c r="F7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">汰
 㳞</t>
         </is>
       </c>
-      <c r="G7" s="11" t="inlineStr">
+      <c r="G7" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">어</t>
         </is>
       </c>
-      <c r="H7" s="17" t="inlineStr">
+      <c r="H7" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">△
 汰</t>
         </is>
       </c>
-      <c r="I7" s="8" t="inlineStr">
+      <c r="I7" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">남</t>
         </is>
       </c>
-      <c r="J7" s="17" t="inlineStr">
+      <c r="J7" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">汰
 汰</t>
         </is>
       </c>
-      <c r="K7" s="8" t="inlineStr">
+      <c r="K7" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">에</t>
         </is>
       </c>
-      <c r="L7" s="17" t="inlineStr">
+      <c r="L7" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">汰
 㳞</t>
         </is>
       </c>
-      <c r="M7" s="8" t="inlineStr">
+      <c r="M7" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">구</t>
         </is>
       </c>
-      <c r="N7" s="17" t="inlineStr">
+      <c r="N7" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="O7" s="8"/>
-      <c r="P7" s="17" t="inlineStr">
+      <c r="O7" s="24"/>
+      <c r="P7" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="Q7" s="8"/>
+      <c r="Q7" s="24"/>
     </row>
     <row r="8" ht="56" customHeight="1">
       <c r="A8" s="0"/>
-      <c r="B8" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="C8" s="9"/>
-      <c r="D8" s="17" t="inlineStr">
+      <c r="B8" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="C8" s="26"/>
+      <c r="D8" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
 汰</t>
         </is>
       </c>
-      <c r="E8" s="9" t="inlineStr">
+      <c r="E8" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">씨</t>
         </is>
       </c>
-      <c r="F8" s="17" t="inlineStr">
+      <c r="F8" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 黃</t>
         </is>
       </c>
-      <c r="G8" s="9"/>
-      <c r="H8" s="18" t="inlineStr">
+      <c r="G8" s="26"/>
+      <c r="H8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞
 潢</t>
         </is>
       </c>
-      <c r="I8" s="12" t="inlineStr">
+      <c r="I8" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">이</t>
         </is>
       </c>
-      <c r="J8" s="17" t="inlineStr">
+      <c r="J8" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">汰</t>
         </is>
       </c>
-      <c r="K8" s="9"/>
-      <c r="L8" s="17" t="inlineStr">
+      <c r="K8" s="26"/>
+      <c r="L8" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 姑</t>
         </is>
       </c>
-      <c r="M8" s="9"/>
-      <c r="N8" s="17" t="inlineStr">
+      <c r="M8" s="26"/>
+      <c r="N8" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 △</t>
         </is>
       </c>
-      <c r="O8" s="9"/>
-      <c r="P8" s="17" t="inlineStr">
+      <c r="O8" s="26"/>
+      <c r="P8" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 △</t>
         </is>
       </c>
-      <c r="Q8" s="9"/>
+      <c r="Q8" s="26"/>
     </row>
     <row r="9" ht="56" customHeight="1">
       <c r="A9" s="0"/>
-      <c r="B9" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="C9" s="9" t="inlineStr">
+      <c r="B9" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="C9" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">남</t>
         </is>
       </c>
-      <c r="D9" s="18" t="inlineStr">
+      <c r="D9" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞
 黃</t>
         </is>
       </c>
-      <c r="E9" s="12" t="inlineStr">
+      <c r="E9" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">구</t>
         </is>
       </c>
-      <c r="F9" s="17" t="inlineStr">
+      <c r="F9" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 姑</t>
         </is>
       </c>
-      <c r="G9" s="9" t="inlineStr">
+      <c r="G9" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">제</t>
         </is>
       </c>
-      <c r="H9" s="18" t="inlineStr">
+      <c r="H9" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 無</t>
         </is>
       </c>
-      <c r="I9" s="12" t="inlineStr">
+      <c r="I9" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">되</t>
         </is>
       </c>
-      <c r="J9" s="17" t="inlineStr">
+      <c r="J9" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">汰
 汰</t>
         </is>
       </c>
-      <c r="K9" s="9" t="inlineStr">
+      <c r="K9" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">인</t>
         </is>
       </c>
-      <c r="L9" s="18" t="inlineStr">
+      <c r="L9" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 姑</t>
         </is>
       </c>
-      <c r="M9" s="12" t="inlineStr">
+      <c r="M9" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">진</t>
         </is>
       </c>
-      <c r="N9" s="17" t="inlineStr">
+      <c r="N9" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
 姑</t>
         </is>
       </c>
-      <c r="O9" s="9" t="inlineStr">
+      <c r="O9" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">길</t>
         </is>
       </c>
-      <c r="P9" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="Q9" s="9"/>
+      <c r="P9" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="Q9" s="26"/>
     </row>
     <row r="10" ht="56" customHeight="1">
       <c r="A10" s="0"/>
-      <c r="B10" s="17" t="inlineStr">
+      <c r="B10" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 姑</t>
         </is>
       </c>
-      <c r="C10" s="10"/>
-      <c r="D10" s="17" t="inlineStr">
+      <c r="C10" s="27"/>
+      <c r="D10" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 無</t>
         </is>
       </c>
-      <c r="E10" s="10"/>
-      <c r="F10" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="G10" s="10" t="inlineStr">
+      <c r="E10" s="27"/>
+      <c r="F10" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="G10" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">이</t>
         </is>
       </c>
-      <c r="H10" s="17" t="inlineStr">
+      <c r="H10" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">黃
 姑</t>
         </is>
       </c>
-      <c r="I10" s="10"/>
-      <c r="J10" s="17" t="inlineStr">
+      <c r="I10" s="27"/>
+      <c r="J10" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">汰</t>
         </is>
       </c>
-      <c r="K10" s="10"/>
-      <c r="L10" s="17" t="inlineStr">
+      <c r="K10" s="27"/>
+      <c r="L10" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">黃
 姑</t>
         </is>
       </c>
-      <c r="M10" s="10" t="inlineStr">
+      <c r="M10" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">터</t>
         </is>
       </c>
-      <c r="N10" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="O10" s="10" t="inlineStr">
+      <c r="N10" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="O10" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">을</t>
         </is>
       </c>
-      <c r="P10" s="18" t="inlineStr">
+      <c r="P10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 姑</t>
         </is>
       </c>
-      <c r="Q10" s="13"/>
+      <c r="Q10" s="28"/>
     </row>
     <row r="11" ht="56" customHeight="1">
       <c r="A11" s="0"/>
-      <c r="B11" s="18" t="inlineStr">
+      <c r="B11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 姑</t>
         </is>
       </c>
-      <c r="C11" s="11" t="inlineStr">
+      <c r="C11" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">지</t>
         </is>
       </c>
-      <c r="D11" s="17" t="inlineStr">
+      <c r="D11" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
 姑</t>
         </is>
       </c>
-      <c r="E11" s="8" t="inlineStr">
+      <c r="E11" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">지</t>
         </is>
       </c>
-      <c r="F11" s="18" t="inlineStr">
+      <c r="F11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 姑</t>
         </is>
       </c>
-      <c r="G11" s="11" t="inlineStr">
+      <c r="G11" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">뽑</t>
         </is>
       </c>
-      <c r="H11" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="I11" s="8" t="inlineStr">
+      <c r="H11" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="I11" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">고</t>
         </is>
       </c>
-      <c r="J11" s="17" t="inlineStr">
+      <c r="J11" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">汰
 汰</t>
         </is>
       </c>
-      <c r="K11" s="8" t="inlineStr">
+      <c r="K11" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">정</t>
         </is>
       </c>
-      <c r="L11" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="M11" s="8" t="inlineStr">
+      <c r="L11" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="M11" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">를</t>
         </is>
       </c>
-      <c r="N11" s="18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="O11" s="11" t="inlineStr">
+      <c r="N11" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="O11" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">갈</t>
         </is>
       </c>
-      <c r="P11" s="17" t="inlineStr">
+      <c r="P11" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 姑</t>
         </is>
       </c>
-      <c r="Q11" s="8" t="inlineStr">
+      <c r="Q11" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">노</t>
         </is>
@@ -6280,143 +6321,143 @@
     </row>
     <row r="12" ht="56" customHeight="1">
       <c r="A12" s="0"/>
-      <c r="B12" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="C12" s="9"/>
-      <c r="D12" s="17" t="inlineStr">
+      <c r="B12" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="C12" s="26"/>
+      <c r="D12" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
 仲</t>
         </is>
       </c>
-      <c r="E12" s="9" t="inlineStr">
+      <c r="E12" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">화</t>
         </is>
       </c>
-      <c r="F12" s="17" t="inlineStr">
+      <c r="F12" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="G12" s="9"/>
-      <c r="H12" s="17" t="inlineStr">
+      <c r="G12" s="26"/>
+      <c r="H12" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 仲</t>
         </is>
       </c>
-      <c r="I12" s="9" t="inlineStr">
+      <c r="I12" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">보</t>
         </is>
       </c>
-      <c r="J12" s="17" t="inlineStr">
+      <c r="J12" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">汰</t>
         </is>
       </c>
-      <c r="K12" s="9"/>
-      <c r="L12" s="17" t="inlineStr">
+      <c r="K12" s="26"/>
+      <c r="L12" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 姑</t>
         </is>
       </c>
-      <c r="M12" s="9" t="inlineStr">
+      <c r="M12" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">보</t>
         </is>
       </c>
-      <c r="N12" s="17" t="inlineStr">
+      <c r="N12" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">△
 姑</t>
         </is>
       </c>
-      <c r="O12" s="9"/>
-      <c r="P12" s="17" t="inlineStr">
+      <c r="O12" s="26"/>
+      <c r="P12" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="Q12" s="9"/>
+      <c r="Q12" s="26"/>
     </row>
     <row r="13" ht="56" customHeight="1">
       <c r="A13" s="0"/>
-      <c r="B13" s="18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="C13" s="12" t="inlineStr">
+      <c r="B13" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="C13" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">마</t>
         </is>
       </c>
-      <c r="D13" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="E13" s="9" t="inlineStr">
+      <c r="D13" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="E13" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">자</t>
         </is>
       </c>
-      <c r="F13" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="G13" s="9" t="inlineStr">
+      <c r="F13" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="G13" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">수</t>
         </is>
       </c>
-      <c r="H13" s="18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="I13" s="12"/>
-      <c r="J13" s="17" t="inlineStr">
+      <c r="H13" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="I13" s="25"/>
+      <c r="J13" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">汰</t>
         </is>
       </c>
-      <c r="K13" s="9" t="inlineStr">
+      <c r="K13" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">리</t>
         </is>
       </c>
-      <c r="L13" s="17" t="inlineStr">
+      <c r="L13" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="M13" s="9"/>
-      <c r="N13" s="17" t="inlineStr">
+      <c r="M13" s="26"/>
+      <c r="N13" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 姑</t>
         </is>
       </c>
-      <c r="O13" s="9" t="inlineStr">
+      <c r="O13" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">적</t>
         </is>
       </c>
-      <c r="P13" s="17" t="inlineStr">
+      <c r="P13" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
 無</t>
         </is>
       </c>
-      <c r="Q13" s="9" t="inlineStr">
+      <c r="Q13" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">지</t>
         </is>
@@ -6424,76 +6465,76 @@
     </row>
     <row r="14" ht="56" customHeight="1">
       <c r="A14" s="0"/>
-      <c r="B14" s="17" t="inlineStr">
+      <c r="B14" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 姑</t>
         </is>
       </c>
-      <c r="C14" s="10"/>
-      <c r="D14" s="17" t="inlineStr">
+      <c r="C14" s="27"/>
+      <c r="D14" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 無</t>
         </is>
       </c>
-      <c r="E14" s="10"/>
-      <c r="F14" s="17" t="inlineStr">
+      <c r="E14" s="27"/>
+      <c r="F14" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 姑</t>
         </is>
       </c>
-      <c r="G14" s="10" t="inlineStr">
+      <c r="G14" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">가</t>
         </is>
       </c>
-      <c r="H14" s="17" t="inlineStr">
+      <c r="H14" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 姑</t>
         </is>
       </c>
-      <c r="I14" s="10" t="inlineStr">
+      <c r="I14" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">면</t>
         </is>
       </c>
-      <c r="J14" s="17" t="inlineStr">
+      <c r="J14" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">汰</t>
         </is>
       </c>
-      <c r="K14" s="10"/>
-      <c r="L14" s="17" t="inlineStr">
+      <c r="K14" s="27"/>
+      <c r="L14" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 姑</t>
         </is>
       </c>
-      <c r="M14" s="10" t="inlineStr">
+      <c r="M14" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">고</t>
         </is>
       </c>
-      <c r="N14" s="17" t="inlineStr">
+      <c r="N14" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="O14" s="10" t="inlineStr">
+      <c r="O14" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">에</t>
         </is>
       </c>
-      <c r="P14" s="17" t="inlineStr">
+      <c r="P14" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
 潢</t>
         </is>
       </c>
-      <c r="Q14" s="10" t="inlineStr">
+      <c r="Q14" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">는</t>
         </is>
@@ -6501,81 +6542,81 @@
     </row>
     <row r="15" ht="56" customHeight="1">
       <c r="A15" s="0"/>
-      <c r="B15" s="18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="C15" s="11" t="inlineStr">
+      <c r="B15" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="C15" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">라</t>
         </is>
       </c>
-      <c r="D15" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="E15" s="8" t="inlineStr">
+      <c r="D15" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="E15" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">좋</t>
         </is>
       </c>
-      <c r="F15" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="G15" s="8" t="inlineStr">
+      <c r="F15" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="G15" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">왔</t>
         </is>
       </c>
-      <c r="H15" s="18" t="inlineStr">
+      <c r="H15" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 潢</t>
         </is>
       </c>
-      <c r="I15" s="11" t="inlineStr">
+      <c r="I15" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">후</t>
         </is>
       </c>
-      <c r="J15" s="17" t="inlineStr">
+      <c r="J15" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">汰
 –</t>
         </is>
       </c>
-      <c r="K15" s="8" t="inlineStr">
+      <c r="K15" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">고</t>
         </is>
       </c>
-      <c r="L15" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="M15" s="8"/>
-      <c r="N15" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="O15" s="8" t="inlineStr">
+      <c r="L15" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="M15" s="24"/>
+      <c r="N15" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="O15" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">이</t>
         </is>
       </c>
-      <c r="P15" s="17" t="inlineStr">
+      <c r="P15" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 仲</t>
         </is>
       </c>
-      <c r="Q15" s="8" t="inlineStr">
+      <c r="Q15" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">못</t>
         </is>
@@ -6583,71 +6624,71 @@
     </row>
     <row r="16" ht="56" customHeight="1">
       <c r="A16" s="0"/>
-      <c r="B16" s="17" t="inlineStr">
+      <c r="B16" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 姑</t>
         </is>
       </c>
-      <c r="C16" s="9"/>
-      <c r="D16" s="17" t="inlineStr">
+      <c r="C16" s="26"/>
+      <c r="D16" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 姑</t>
         </is>
       </c>
-      <c r="E16" s="9"/>
-      <c r="F16" s="17" t="inlineStr">
+      <c r="E16" s="26"/>
+      <c r="F16" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 姑</t>
         </is>
       </c>
-      <c r="G16" s="9"/>
-      <c r="H16" s="17" t="inlineStr">
+      <c r="G16" s="26"/>
+      <c r="H16" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="I16" s="9" t="inlineStr">
+      <c r="I16" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">회</t>
         </is>
       </c>
-      <c r="J16" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="K16" s="9" t="inlineStr">
+      <c r="J16" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="K16" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">는</t>
         </is>
       </c>
-      <c r="L16" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="M16" s="9"/>
-      <c r="N16" s="18" t="inlineStr">
+      <c r="L16" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="M16" s="26"/>
+      <c r="N16" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
 仲</t>
         </is>
       </c>
-      <c r="O16" s="12" t="inlineStr">
+      <c r="O16" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">상</t>
         </is>
       </c>
-      <c r="P16" s="17" t="inlineStr">
+      <c r="P16" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
 仲</t>
         </is>
       </c>
-      <c r="Q16" s="9" t="inlineStr">
+      <c r="Q16" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">하</t>
         </is>
@@ -6655,77 +6696,77 @@
     </row>
     <row r="17" ht="56" customHeight="1">
       <c r="A17" s="0"/>
-      <c r="B17" s="17" t="inlineStr">
+      <c r="B17" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">△</t>
         </is>
       </c>
-      <c r="C17" s="9" t="inlineStr">
+      <c r="C17" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">정</t>
         </is>
       </c>
-      <c r="D17" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="E17" s="9" t="inlineStr">
+      <c r="D17" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="E17" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">네</t>
         </is>
       </c>
-      <c r="F17" s="18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="G17" s="12" t="inlineStr">
+      <c r="F17" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="G17" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">으</t>
         </is>
       </c>
-      <c r="H17" s="17" t="inlineStr">
+      <c r="H17" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 姑</t>
         </is>
       </c>
-      <c r="I17" s="9" t="inlineStr">
+      <c r="I17" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">막</t>
         </is>
       </c>
-      <c r="J17" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="K17" s="9"/>
-      <c r="L17" s="17" t="inlineStr">
+      <c r="J17" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="K17" s="26"/>
+      <c r="L17" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 姑</t>
         </is>
       </c>
-      <c r="M17" s="9"/>
-      <c r="N17" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="O17" s="9" t="inlineStr">
+      <c r="M17" s="26"/>
+      <c r="N17" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="O17" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">한</t>
         </is>
       </c>
-      <c r="P17" s="17" t="inlineStr">
+      <c r="P17" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
 –</t>
         </is>
       </c>
-      <c r="Q17" s="9" t="inlineStr">
+      <c r="Q17" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">리</t>
         </is>
@@ -6733,75 +6774,75 @@
     </row>
     <row r="18" ht="56" customHeight="1">
       <c r="A18" s="0"/>
-      <c r="B18" s="18" t="inlineStr">
+      <c r="B18" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 潢</t>
         </is>
       </c>
-      <c r="C18" s="13" t="inlineStr">
+      <c r="C18" s="28" t="inlineStr">
         <is>
           <t xml:space="preserve">상</t>
         </is>
       </c>
-      <c r="D18" s="18" t="inlineStr">
+      <c r="D18" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">△</t>
         </is>
       </c>
-      <c r="E18" s="13" t="inlineStr">
+      <c r="E18" s="28" t="inlineStr">
         <is>
           <t xml:space="preserve">아?</t>
         </is>
       </c>
-      <c r="F18" s="18" t="inlineStr">
+      <c r="F18" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 姑</t>
         </is>
       </c>
-      <c r="G18" s="13" t="inlineStr">
+      <c r="G18" s="28" t="inlineStr">
         <is>
           <t xml:space="preserve">니</t>
         </is>
       </c>
-      <c r="H18" s="17" t="inlineStr">
+      <c r="H18" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="I18" s="10" t="inlineStr">
+      <c r="I18" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">금</t>
         </is>
       </c>
-      <c r="J18" s="17" t="inlineStr">
+      <c r="J18" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 姑</t>
         </is>
       </c>
-      <c r="K18" s="10"/>
-      <c r="L18" s="18" t="inlineStr">
+      <c r="K18" s="27"/>
+      <c r="L18" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
 姑</t>
         </is>
       </c>
-      <c r="M18" s="13"/>
-      <c r="N18" s="17" t="inlineStr">
+      <c r="M18" s="28"/>
+      <c r="N18" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 姑</t>
         </is>
       </c>
-      <c r="O18" s="10"/>
-      <c r="P18" s="17" t="inlineStr">
+      <c r="O18" s="27"/>
+      <c r="P18" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">△</t>
         </is>
       </c>
-      <c r="Q18" s="10" t="inlineStr">
+      <c r="Q18" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">라</t>
         </is>

--- a/sheets/민요/검수/창부타령 1.xlsx
+++ b/sheets/민요/검수/창부타령 1.xlsx
@@ -5586,28 +5586,28 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
-    <col min="2" max="2" width="9" customWidth="1"/>
+    <col min="2" max="2" width="12" customWidth="1"/>
     <col min="3" max="3" width="6" customWidth="1"/>
-    <col min="4" max="4" width="9" customWidth="1"/>
+    <col min="4" max="4" width="12" customWidth="1"/>
     <col min="5" max="5" width="6" customWidth="1"/>
-    <col min="6" max="6" width="9" customWidth="1"/>
+    <col min="6" max="6" width="12" customWidth="1"/>
     <col min="7" max="7" width="6" customWidth="1"/>
-    <col min="8" max="8" width="9" customWidth="1"/>
+    <col min="8" max="8" width="12" customWidth="1"/>
     <col min="9" max="9" width="6" customWidth="1"/>
-    <col min="10" max="10" width="9" customWidth="1"/>
+    <col min="10" max="10" width="12" customWidth="1"/>
     <col min="11" max="11" width="6" customWidth="1"/>
-    <col min="12" max="12" width="9" customWidth="1"/>
+    <col min="12" max="12" width="12" customWidth="1"/>
     <col min="13" max="13" width="6" customWidth="1"/>
-    <col min="14" max="14" width="9" customWidth="1"/>
+    <col min="14" max="14" width="12" customWidth="1"/>
     <col min="15" max="15" width="6" customWidth="1"/>
-    <col min="16" max="16" width="9" customWidth="1"/>
+    <col min="16" max="16" width="12" customWidth="1"/>
     <col min="17" max="17" width="6" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="0"/>
     </row>
-    <row r="2" ht="60" customHeight="1">
+    <row r="2" ht="82.06" customHeight="1">
       <c r="A2" s="0"/>
       <c r="B2" s="20" t="inlineStr">
         <is>
@@ -5630,7 +5630,7 @@
       <c r="P2" s="20"/>
       <c r="Q2" s="20"/>
     </row>
-    <row r="3" ht="56" customHeight="1">
+    <row r="3" ht="82.06" customHeight="1">
       <c r="A3" s="0"/>
       <c r="B3" s="21" t="inlineStr">
         <is>
@@ -5719,7 +5719,7 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="56" customHeight="1">
+    <row r="4" ht="82.06" customHeight="1">
       <c r="A4" s="0"/>
       <c r="B4" s="21" t="inlineStr">
         <is>
@@ -5795,7 +5795,7 @@
       </c>
       <c r="Q4" s="26"/>
     </row>
-    <row r="5" ht="56" customHeight="1">
+    <row r="5" ht="82.06" customHeight="1">
       <c r="A5" s="0"/>
       <c r="B5" s="23" t="inlineStr">
         <is>
@@ -5876,11 +5876,11 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="56" customHeight="1">
+    <row r="6" ht="82.06" customHeight="1">
       <c r="A6" s="0"/>
       <c r="B6" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="C6" s="27"/>
@@ -5892,13 +5892,13 @@
       <c r="E6" s="27"/>
       <c r="F6" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="G6" s="27"/>
       <c r="H6" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I6" s="27"/>
@@ -5921,18 +5921,18 @@
       </c>
       <c r="N6" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="O6" s="27"/>
       <c r="P6" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="Q6" s="27"/>
     </row>
-    <row r="7" ht="56" customHeight="1">
+    <row r="7" ht="82.06" customHeight="1">
       <c r="A7" s="0"/>
       <c r="B7" s="23" t="inlineStr">
         <is>
@@ -6013,7 +6013,7 @@
       </c>
       <c r="Q7" s="24"/>
     </row>
-    <row r="8" ht="56" customHeight="1">
+    <row r="8" ht="82.06" customHeight="1">
       <c r="A8" s="0"/>
       <c r="B8" s="23" t="inlineStr">
         <is>
@@ -6078,7 +6078,7 @@
       </c>
       <c r="Q8" s="26"/>
     </row>
-    <row r="9" ht="56" customHeight="1">
+    <row r="9" ht="82.06" customHeight="1">
       <c r="A9" s="0"/>
       <c r="B9" s="23" t="inlineStr">
         <is>
@@ -6163,7 +6163,7 @@
       </c>
       <c r="Q9" s="26"/>
     </row>
-    <row r="10" ht="56" customHeight="1">
+    <row r="10" ht="82.06" customHeight="1">
       <c r="A10" s="0"/>
       <c r="B10" s="23" t="inlineStr">
         <is>
@@ -6231,7 +6231,7 @@
       </c>
       <c r="Q10" s="28"/>
     </row>
-    <row r="11" ht="56" customHeight="1">
+    <row r="11" ht="82.06" customHeight="1">
       <c r="A11" s="0"/>
       <c r="B11" s="21" t="inlineStr">
         <is>
@@ -6319,7 +6319,7 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="56" customHeight="1">
+    <row r="12" ht="82.06" customHeight="1">
       <c r="A12" s="0"/>
       <c r="B12" s="23" t="inlineStr">
         <is>
@@ -6386,7 +6386,7 @@
       </c>
       <c r="Q12" s="26"/>
     </row>
-    <row r="13" ht="56" customHeight="1">
+    <row r="13" ht="82.06" customHeight="1">
       <c r="A13" s="0"/>
       <c r="B13" s="21" t="inlineStr">
         <is>
@@ -6463,7 +6463,7 @@
         </is>
       </c>
     </row>
-    <row r="14" ht="56" customHeight="1">
+    <row r="14" ht="82.06" customHeight="1">
       <c r="A14" s="0"/>
       <c r="B14" s="23" t="inlineStr">
         <is>
@@ -6540,7 +6540,7 @@
         </is>
       </c>
     </row>
-    <row r="15" ht="56" customHeight="1">
+    <row r="15" ht="82.06" customHeight="1">
       <c r="A15" s="0"/>
       <c r="B15" s="21" t="inlineStr">
         <is>
@@ -6622,7 +6622,7 @@
         </is>
       </c>
     </row>
-    <row r="16" ht="56" customHeight="1">
+    <row r="16" ht="82.06" customHeight="1">
       <c r="A16" s="0"/>
       <c r="B16" s="23" t="inlineStr">
         <is>
@@ -6694,7 +6694,7 @@
         </is>
       </c>
     </row>
-    <row r="17" ht="56" customHeight="1">
+    <row r="17" ht="82.06" customHeight="1">
       <c r="A17" s="0"/>
       <c r="B17" s="23" t="inlineStr">
         <is>
@@ -6772,7 +6772,7 @@
         </is>
       </c>
     </row>
-    <row r="18" ht="56" customHeight="1">
+    <row r="18" ht="82.06" customHeight="1">
       <c r="A18" s="0"/>
       <c r="B18" s="21" t="inlineStr">
         <is>

--- a/sheets/민요/검수/창부타령 1.xlsx
+++ b/sheets/민요/검수/창부타령 1.xlsx
@@ -6792,7 +6792,8 @@
       </c>
       <c r="E18" s="28" t="inlineStr">
         <is>
-          <t xml:space="preserve">아?</t>
+          <t xml:space="preserve">아
+?</t>
         </is>
       </c>
       <c r="F18" s="21" t="inlineStr">

--- a/sheets/민요/검수/창부타령 1.xlsx
+++ b/sheets/민요/검수/창부타령 1.xlsx
@@ -11,7 +11,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="7">
+  <fonts count="8">
     <font>
       <sz val="11"/>
       <name val="궁서체"/>
@@ -47,6 +47,11 @@
     </font>
     <font>
       <sz val="12"/>
+      <name val="궁서체"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="18"/>
       <name val="궁서체"/>
       <family val="2"/>
     </font>
@@ -150,7 +155,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="35">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -236,6 +241,24 @@
     <xf numFmtId="0" fontId="6" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -5638,7 +5661,7 @@
 姑</t>
         </is>
       </c>
-      <c r="C3" s="22" t="inlineStr">
+      <c r="C3" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">백</t>
         </is>
@@ -5649,7 +5672,7 @@
 潢</t>
         </is>
       </c>
-      <c r="E3" s="22" t="inlineStr">
+      <c r="E3" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">얼</t>
         </is>
@@ -5660,7 +5683,7 @@
 黃</t>
         </is>
       </c>
-      <c r="G3" s="22" t="inlineStr">
+      <c r="G3" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">이</t>
         </is>
@@ -5671,7 +5694,7 @@
 黃</t>
         </is>
       </c>
-      <c r="I3" s="22" t="inlineStr">
+      <c r="I3" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">일</t>
         </is>
@@ -5681,7 +5704,7 @@
           <t xml:space="preserve">汰汰</t>
         </is>
       </c>
-      <c r="K3" s="22" t="inlineStr">
+      <c r="K3" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">새</t>
         </is>
@@ -5691,7 +5714,7 @@
           <t xml:space="preserve">△</t>
         </is>
       </c>
-      <c r="M3" s="24" t="inlineStr">
+      <c r="M3" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">하</t>
         </is>
@@ -5702,7 +5725,7 @@
 姑</t>
         </is>
       </c>
-      <c r="O3" s="22" t="inlineStr">
+      <c r="O3" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">우</t>
         </is>
@@ -5713,7 +5736,7 @@
 姑</t>
         </is>
       </c>
-      <c r="Q3" s="22" t="inlineStr">
+      <c r="Q3" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">아</t>
         </is>
@@ -5726,14 +5749,14 @@
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="C4" s="25"/>
+      <c r="C4" s="31"/>
       <c r="D4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
 㳞</t>
         </is>
       </c>
-      <c r="E4" s="25" t="inlineStr">
+      <c r="E4" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">씨</t>
         </is>
@@ -5743,7 +5766,7 @@
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="G4" s="26" t="inlineStr">
+      <c r="G4" s="32" t="inlineStr">
         <is>
           <t xml:space="preserve">까</t>
         </is>
@@ -5754,7 +5777,7 @@
 姑</t>
         </is>
       </c>
-      <c r="I4" s="26" t="inlineStr">
+      <c r="I4" s="32" t="inlineStr">
         <is>
           <t xml:space="preserve">구</t>
         </is>
@@ -5764,7 +5787,7 @@
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="K4" s="26"/>
+      <c r="K4" s="32"/>
       <c r="L4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無
@@ -5772,7 +5795,7 @@
 汰</t>
         </is>
       </c>
-      <c r="M4" s="25" t="inlineStr">
+      <c r="M4" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">아</t>
         </is>
@@ -5783,7 +5806,7 @@
 姑</t>
         </is>
       </c>
-      <c r="O4" s="26" t="inlineStr">
+      <c r="O4" s="32" t="inlineStr">
         <is>
           <t xml:space="preserve">련</t>
         </is>
@@ -5793,7 +5816,7 @@
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="Q4" s="26"/>
+      <c r="Q4" s="32"/>
     </row>
     <row r="5" ht="82.06" customHeight="1">
       <c r="A5" s="0"/>
@@ -5802,7 +5825,7 @@
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="C5" s="26" t="inlineStr">
+      <c r="C5" s="32" t="inlineStr">
         <is>
           <t xml:space="preserve">구</t>
         </is>
@@ -5813,7 +5836,7 @@
 仲</t>
         </is>
       </c>
-      <c r="E5" s="26" t="inlineStr">
+      <c r="E5" s="32" t="inlineStr">
         <is>
           <t xml:space="preserve">구</t>
         </is>
@@ -5823,7 +5846,7 @@
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="G5" s="26" t="inlineStr">
+      <c r="G5" s="32" t="inlineStr">
         <is>
           <t xml:space="preserve">지</t>
         </is>
@@ -5833,7 +5856,7 @@
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="I5" s="26" t="inlineStr">
+      <c r="I5" s="32" t="inlineStr">
         <is>
           <t xml:space="preserve">에</t>
         </is>
@@ -5844,7 +5867,7 @@
 –</t>
         </is>
       </c>
-      <c r="K5" s="26" t="inlineStr">
+      <c r="K5" s="32" t="inlineStr">
         <is>
           <t xml:space="preserve">람</t>
         </is>
@@ -5854,13 +5877,13 @@
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="M5" s="26"/>
+      <c r="M5" s="32"/>
       <c r="N5" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="O5" s="26" t="inlineStr">
+      <c r="O5" s="32" t="inlineStr">
         <is>
           <t xml:space="preserve">이</t>
         </is>
@@ -5870,7 +5893,7 @@
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="Q5" s="26" t="inlineStr">
+      <c r="Q5" s="32" t="inlineStr">
         <is>
           <t xml:space="preserve">니</t>
         </is>
@@ -5883,38 +5906,38 @@
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="C6" s="27"/>
+      <c r="C6" s="33"/>
       <c r="D6" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="E6" s="27"/>
+      <c r="E6" s="33"/>
       <c r="F6" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="G6" s="27"/>
+      <c r="G6" s="33"/>
       <c r="H6" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="I6" s="27"/>
+      <c r="I6" s="33"/>
       <c r="J6" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">△</t>
         </is>
       </c>
-      <c r="K6" s="27"/>
+      <c r="K6" s="33"/>
       <c r="L6" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞
 姑</t>
         </is>
       </c>
-      <c r="M6" s="28" t="inlineStr">
+      <c r="M6" s="34" t="inlineStr">
         <is>
           <t xml:space="preserve">구</t>
         </is>
@@ -5924,13 +5947,13 @@
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="O6" s="27"/>
+      <c r="O6" s="33"/>
       <c r="P6" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="Q6" s="27"/>
+      <c r="Q6" s="33"/>
     </row>
     <row r="7" ht="82.06" customHeight="1">
       <c r="A7" s="0"/>
@@ -5940,7 +5963,7 @@
 姑</t>
         </is>
       </c>
-      <c r="C7" s="24" t="inlineStr">
+      <c r="C7" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">야</t>
         </is>
@@ -5951,7 +5974,7 @@
 潢</t>
         </is>
       </c>
-      <c r="E7" s="22" t="inlineStr">
+      <c r="E7" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">절</t>
         </is>
@@ -5962,7 +5985,7 @@
 㳞</t>
         </is>
       </c>
-      <c r="G7" s="22" t="inlineStr">
+      <c r="G7" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">어</t>
         </is>
@@ -5973,7 +5996,7 @@
 汰</t>
         </is>
       </c>
-      <c r="I7" s="24" t="inlineStr">
+      <c r="I7" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">남</t>
         </is>
@@ -5984,7 +6007,7 @@
 汰</t>
         </is>
       </c>
-      <c r="K7" s="24" t="inlineStr">
+      <c r="K7" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">에</t>
         </is>
@@ -5995,7 +6018,7 @@
 㳞</t>
         </is>
       </c>
-      <c r="M7" s="24" t="inlineStr">
+      <c r="M7" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">구</t>
         </is>
@@ -6005,13 +6028,13 @@
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="O7" s="24"/>
+      <c r="O7" s="30"/>
       <c r="P7" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="Q7" s="24"/>
+      <c r="Q7" s="30"/>
     </row>
     <row r="8" ht="82.06" customHeight="1">
       <c r="A8" s="0"/>
@@ -6020,14 +6043,14 @@
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="C8" s="26"/>
+      <c r="C8" s="32"/>
       <c r="D8" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
 汰</t>
         </is>
       </c>
-      <c r="E8" s="26" t="inlineStr">
+      <c r="E8" s="32" t="inlineStr">
         <is>
           <t xml:space="preserve">씨</t>
         </is>
@@ -6038,14 +6061,14 @@
 黃</t>
         </is>
       </c>
-      <c r="G8" s="26"/>
+      <c r="G8" s="32"/>
       <c r="H8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞
 潢</t>
         </is>
       </c>
-      <c r="I8" s="25" t="inlineStr">
+      <c r="I8" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">이</t>
         </is>
@@ -6055,28 +6078,28 @@
           <t xml:space="preserve">汰</t>
         </is>
       </c>
-      <c r="K8" s="26"/>
+      <c r="K8" s="32"/>
       <c r="L8" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 姑</t>
         </is>
       </c>
-      <c r="M8" s="26"/>
+      <c r="M8" s="32"/>
       <c r="N8" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 △</t>
         </is>
       </c>
-      <c r="O8" s="26"/>
+      <c r="O8" s="32"/>
       <c r="P8" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 △</t>
         </is>
       </c>
-      <c r="Q8" s="26"/>
+      <c r="Q8" s="32"/>
     </row>
     <row r="9" ht="82.06" customHeight="1">
       <c r="A9" s="0"/>
@@ -6085,7 +6108,7 @@
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="C9" s="26" t="inlineStr">
+      <c r="C9" s="32" t="inlineStr">
         <is>
           <t xml:space="preserve">남</t>
         </is>
@@ -6096,7 +6119,7 @@
 黃</t>
         </is>
       </c>
-      <c r="E9" s="25" t="inlineStr">
+      <c r="E9" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">구</t>
         </is>
@@ -6107,7 +6130,7 @@
 姑</t>
         </is>
       </c>
-      <c r="G9" s="26" t="inlineStr">
+      <c r="G9" s="32" t="inlineStr">
         <is>
           <t xml:space="preserve">제</t>
         </is>
@@ -6118,7 +6141,7 @@
 無</t>
         </is>
       </c>
-      <c r="I9" s="25" t="inlineStr">
+      <c r="I9" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">되</t>
         </is>
@@ -6129,7 +6152,7 @@
 汰</t>
         </is>
       </c>
-      <c r="K9" s="26" t="inlineStr">
+      <c r="K9" s="32" t="inlineStr">
         <is>
           <t xml:space="preserve">인</t>
         </is>
@@ -6140,7 +6163,7 @@
 姑</t>
         </is>
       </c>
-      <c r="M9" s="25" t="inlineStr">
+      <c r="M9" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">진</t>
         </is>
@@ -6151,7 +6174,7 @@
 姑</t>
         </is>
       </c>
-      <c r="O9" s="26" t="inlineStr">
+      <c r="O9" s="32" t="inlineStr">
         <is>
           <t xml:space="preserve">길</t>
         </is>
@@ -6161,7 +6184,7 @@
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="Q9" s="26"/>
+      <c r="Q9" s="32"/>
     </row>
     <row r="10" ht="82.06" customHeight="1">
       <c r="A10" s="0"/>
@@ -6171,20 +6194,20 @@
 姑</t>
         </is>
       </c>
-      <c r="C10" s="27"/>
+      <c r="C10" s="33"/>
       <c r="D10" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 無</t>
         </is>
       </c>
-      <c r="E10" s="27"/>
+      <c r="E10" s="33"/>
       <c r="F10" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="G10" s="27" t="inlineStr">
+      <c r="G10" s="33" t="inlineStr">
         <is>
           <t xml:space="preserve">이</t>
         </is>
@@ -6195,20 +6218,20 @@
 姑</t>
         </is>
       </c>
-      <c r="I10" s="27"/>
+      <c r="I10" s="33"/>
       <c r="J10" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">汰</t>
         </is>
       </c>
-      <c r="K10" s="27"/>
+      <c r="K10" s="33"/>
       <c r="L10" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">黃
 姑</t>
         </is>
       </c>
-      <c r="M10" s="27" t="inlineStr">
+      <c r="M10" s="33" t="inlineStr">
         <is>
           <t xml:space="preserve">터</t>
         </is>
@@ -6218,7 +6241,7 @@
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="O10" s="27" t="inlineStr">
+      <c r="O10" s="33" t="inlineStr">
         <is>
           <t xml:space="preserve">을</t>
         </is>
@@ -6229,7 +6252,7 @@
 姑</t>
         </is>
       </c>
-      <c r="Q10" s="28"/>
+      <c r="Q10" s="34"/>
     </row>
     <row r="11" ht="82.06" customHeight="1">
       <c r="A11" s="0"/>
@@ -6239,7 +6262,7 @@
 姑</t>
         </is>
       </c>
-      <c r="C11" s="22" t="inlineStr">
+      <c r="C11" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">지</t>
         </is>
@@ -6250,7 +6273,7 @@
 姑</t>
         </is>
       </c>
-      <c r="E11" s="24" t="inlineStr">
+      <c r="E11" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">지</t>
         </is>
@@ -6261,7 +6284,7 @@
 姑</t>
         </is>
       </c>
-      <c r="G11" s="22" t="inlineStr">
+      <c r="G11" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">뽑</t>
         </is>
@@ -6271,7 +6294,7 @@
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="I11" s="24" t="inlineStr">
+      <c r="I11" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">고</t>
         </is>
@@ -6282,7 +6305,7 @@
 汰</t>
         </is>
       </c>
-      <c r="K11" s="24" t="inlineStr">
+      <c r="K11" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">정</t>
         </is>
@@ -6292,7 +6315,7 @@
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="M11" s="24" t="inlineStr">
+      <c r="M11" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">를</t>
         </is>
@@ -6302,7 +6325,7 @@
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="O11" s="22" t="inlineStr">
+      <c r="O11" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">갈</t>
         </is>
@@ -6313,7 +6336,7 @@
 姑</t>
         </is>
       </c>
-      <c r="Q11" s="24" t="inlineStr">
+      <c r="Q11" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">노</t>
         </is>
@@ -6326,14 +6349,14 @@
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="C12" s="26"/>
+      <c r="C12" s="32"/>
       <c r="D12" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
 仲</t>
         </is>
       </c>
-      <c r="E12" s="26" t="inlineStr">
+      <c r="E12" s="32" t="inlineStr">
         <is>
           <t xml:space="preserve">화</t>
         </is>
@@ -6343,14 +6366,14 @@
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="G12" s="26"/>
+      <c r="G12" s="32"/>
       <c r="H12" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 仲</t>
         </is>
       </c>
-      <c r="I12" s="26" t="inlineStr">
+      <c r="I12" s="32" t="inlineStr">
         <is>
           <t xml:space="preserve">보</t>
         </is>
@@ -6360,14 +6383,14 @@
           <t xml:space="preserve">汰</t>
         </is>
       </c>
-      <c r="K12" s="26"/>
+      <c r="K12" s="32"/>
       <c r="L12" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 姑</t>
         </is>
       </c>
-      <c r="M12" s="26" t="inlineStr">
+      <c r="M12" s="32" t="inlineStr">
         <is>
           <t xml:space="preserve">보</t>
         </is>
@@ -6378,13 +6401,13 @@
 姑</t>
         </is>
       </c>
-      <c r="O12" s="26"/>
+      <c r="O12" s="32"/>
       <c r="P12" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="Q12" s="26"/>
+      <c r="Q12" s="32"/>
     </row>
     <row r="13" ht="82.06" customHeight="1">
       <c r="A13" s="0"/>
@@ -6393,7 +6416,7 @@
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="C13" s="25" t="inlineStr">
+      <c r="C13" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">마</t>
         </is>
@@ -6403,7 +6426,7 @@
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="E13" s="26" t="inlineStr">
+      <c r="E13" s="32" t="inlineStr">
         <is>
           <t xml:space="preserve">자</t>
         </is>
@@ -6413,7 +6436,7 @@
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="G13" s="26" t="inlineStr">
+      <c r="G13" s="32" t="inlineStr">
         <is>
           <t xml:space="preserve">수</t>
         </is>
@@ -6423,13 +6446,13 @@
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="I13" s="25"/>
+      <c r="I13" s="31"/>
       <c r="J13" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">汰</t>
         </is>
       </c>
-      <c r="K13" s="26" t="inlineStr">
+      <c r="K13" s="32" t="inlineStr">
         <is>
           <t xml:space="preserve">리</t>
         </is>
@@ -6439,14 +6462,14 @@
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="M13" s="26"/>
+      <c r="M13" s="32"/>
       <c r="N13" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 姑</t>
         </is>
       </c>
-      <c r="O13" s="26" t="inlineStr">
+      <c r="O13" s="32" t="inlineStr">
         <is>
           <t xml:space="preserve">적</t>
         </is>
@@ -6457,7 +6480,7 @@
 無</t>
         </is>
       </c>
-      <c r="Q13" s="26" t="inlineStr">
+      <c r="Q13" s="32" t="inlineStr">
         <is>
           <t xml:space="preserve">지</t>
         </is>
@@ -6471,21 +6494,21 @@
 姑</t>
         </is>
       </c>
-      <c r="C14" s="27"/>
+      <c r="C14" s="33"/>
       <c r="D14" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 無</t>
         </is>
       </c>
-      <c r="E14" s="27"/>
+      <c r="E14" s="33"/>
       <c r="F14" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 姑</t>
         </is>
       </c>
-      <c r="G14" s="27" t="inlineStr">
+      <c r="G14" s="33" t="inlineStr">
         <is>
           <t xml:space="preserve">가</t>
         </is>
@@ -6496,7 +6519,7 @@
 姑</t>
         </is>
       </c>
-      <c r="I14" s="27" t="inlineStr">
+      <c r="I14" s="33" t="inlineStr">
         <is>
           <t xml:space="preserve">면</t>
         </is>
@@ -6506,14 +6529,14 @@
           <t xml:space="preserve">汰</t>
         </is>
       </c>
-      <c r="K14" s="27"/>
+      <c r="K14" s="33"/>
       <c r="L14" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 姑</t>
         </is>
       </c>
-      <c r="M14" s="27" t="inlineStr">
+      <c r="M14" s="33" t="inlineStr">
         <is>
           <t xml:space="preserve">고</t>
         </is>
@@ -6523,7 +6546,7 @@
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="O14" s="27" t="inlineStr">
+      <c r="O14" s="33" t="inlineStr">
         <is>
           <t xml:space="preserve">에</t>
         </is>
@@ -6534,7 +6557,7 @@
 潢</t>
         </is>
       </c>
-      <c r="Q14" s="27" t="inlineStr">
+      <c r="Q14" s="33" t="inlineStr">
         <is>
           <t xml:space="preserve">는</t>
         </is>
@@ -6547,7 +6570,7 @@
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="C15" s="22" t="inlineStr">
+      <c r="C15" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">라</t>
         </is>
@@ -6557,7 +6580,7 @@
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="E15" s="24" t="inlineStr">
+      <c r="E15" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">좋</t>
         </is>
@@ -6567,7 +6590,7 @@
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="G15" s="24" t="inlineStr">
+      <c r="G15" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">왔</t>
         </is>
@@ -6578,7 +6601,7 @@
 潢</t>
         </is>
       </c>
-      <c r="I15" s="22" t="inlineStr">
+      <c r="I15" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">후</t>
         </is>
@@ -6589,7 +6612,7 @@
 –</t>
         </is>
       </c>
-      <c r="K15" s="24" t="inlineStr">
+      <c r="K15" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">고</t>
         </is>
@@ -6599,13 +6622,13 @@
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="M15" s="24"/>
+      <c r="M15" s="30"/>
       <c r="N15" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="O15" s="24" t="inlineStr">
+      <c r="O15" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">이</t>
         </is>
@@ -6616,7 +6639,7 @@
 仲</t>
         </is>
       </c>
-      <c r="Q15" s="24" t="inlineStr">
+      <c r="Q15" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">못</t>
         </is>
@@ -6630,27 +6653,27 @@
 姑</t>
         </is>
       </c>
-      <c r="C16" s="26"/>
+      <c r="C16" s="32"/>
       <c r="D16" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 姑</t>
         </is>
       </c>
-      <c r="E16" s="26"/>
+      <c r="E16" s="32"/>
       <c r="F16" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 姑</t>
         </is>
       </c>
-      <c r="G16" s="26"/>
+      <c r="G16" s="32"/>
       <c r="H16" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="I16" s="26" t="inlineStr">
+      <c r="I16" s="32" t="inlineStr">
         <is>
           <t xml:space="preserve">회</t>
         </is>
@@ -6660,7 +6683,7 @@
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="K16" s="26" t="inlineStr">
+      <c r="K16" s="32" t="inlineStr">
         <is>
           <t xml:space="preserve">는</t>
         </is>
@@ -6670,14 +6693,14 @@
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="M16" s="26"/>
+      <c r="M16" s="32"/>
       <c r="N16" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
 仲</t>
         </is>
       </c>
-      <c r="O16" s="25" t="inlineStr">
+      <c r="O16" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">상</t>
         </is>
@@ -6688,7 +6711,7 @@
 仲</t>
         </is>
       </c>
-      <c r="Q16" s="26" t="inlineStr">
+      <c r="Q16" s="32" t="inlineStr">
         <is>
           <t xml:space="preserve">하</t>
         </is>
@@ -6701,7 +6724,7 @@
           <t xml:space="preserve">△</t>
         </is>
       </c>
-      <c r="C17" s="26" t="inlineStr">
+      <c r="C17" s="32" t="inlineStr">
         <is>
           <t xml:space="preserve">정</t>
         </is>
@@ -6711,7 +6734,7 @@
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="E17" s="26" t="inlineStr">
+      <c r="E17" s="32" t="inlineStr">
         <is>
           <t xml:space="preserve">네</t>
         </is>
@@ -6721,7 +6744,7 @@
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="G17" s="25" t="inlineStr">
+      <c r="G17" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">으</t>
         </is>
@@ -6732,7 +6755,7 @@
 姑</t>
         </is>
       </c>
-      <c r="I17" s="26" t="inlineStr">
+      <c r="I17" s="32" t="inlineStr">
         <is>
           <t xml:space="preserve">막</t>
         </is>
@@ -6742,20 +6765,20 @@
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="K17" s="26"/>
+      <c r="K17" s="32"/>
       <c r="L17" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 姑</t>
         </is>
       </c>
-      <c r="M17" s="26"/>
+      <c r="M17" s="32"/>
       <c r="N17" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="O17" s="26" t="inlineStr">
+      <c r="O17" s="32" t="inlineStr">
         <is>
           <t xml:space="preserve">한</t>
         </is>
@@ -6766,7 +6789,7 @@
 –</t>
         </is>
       </c>
-      <c r="Q17" s="26" t="inlineStr">
+      <c r="Q17" s="32" t="inlineStr">
         <is>
           <t xml:space="preserve">리</t>
         </is>
@@ -6780,7 +6803,7 @@
 潢</t>
         </is>
       </c>
-      <c r="C18" s="28" t="inlineStr">
+      <c r="C18" s="34" t="inlineStr">
         <is>
           <t xml:space="preserve">상</t>
         </is>
@@ -6790,7 +6813,7 @@
           <t xml:space="preserve">△</t>
         </is>
       </c>
-      <c r="E18" s="28" t="inlineStr">
+      <c r="E18" s="34" t="inlineStr">
         <is>
           <t xml:space="preserve">아
 ?</t>
@@ -6802,7 +6825,7 @@
 姑</t>
         </is>
       </c>
-      <c r="G18" s="28" t="inlineStr">
+      <c r="G18" s="34" t="inlineStr">
         <is>
           <t xml:space="preserve">니</t>
         </is>
@@ -6812,7 +6835,7 @@
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="I18" s="27" t="inlineStr">
+      <c r="I18" s="33" t="inlineStr">
         <is>
           <t xml:space="preserve">금</t>
         </is>
@@ -6823,27 +6846,27 @@
 姑</t>
         </is>
       </c>
-      <c r="K18" s="27"/>
+      <c r="K18" s="33"/>
       <c r="L18" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
 姑</t>
         </is>
       </c>
-      <c r="M18" s="28"/>
+      <c r="M18" s="34"/>
       <c r="N18" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 姑</t>
         </is>
       </c>
-      <c r="O18" s="27"/>
+      <c r="O18" s="33"/>
       <c r="P18" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">△</t>
         </is>
       </c>
-      <c r="Q18" s="27" t="inlineStr">
+      <c r="Q18" s="33" t="inlineStr">
         <is>
           <t xml:space="preserve">라</t>
         </is>

--- a/sheets/민요/검수/창부타령 1.xlsx
+++ b/sheets/민요/검수/창부타령 1.xlsx
@@ -65,10 +65,7 @@
       </patternFill>
     </fill>
     <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFF2CC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="solid">

--- a/sheets/민요/검수/창부타령 1.xlsx
+++ b/sheets/민요/검수/창부타령 1.xlsx
@@ -3217,6 +3217,9 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <pageSetUpPr fitToPage="0"/>
+  </sheetPr>
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
     <col min="2" max="2" width="12" customWidth="1"/>
@@ -3237,10 +3240,10 @@
     <col min="17" max="17" width="6" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="6.0" customHeight="true">
       <c r="A1" s="0"/>
     </row>
-    <row r="2" ht="102.95" customHeight="1">
+    <row r="2" ht="68.97" customHeight="true">
       <c r="A2" s="0"/>
       <c r="B2" s="20" t="inlineStr">
         <is>
@@ -3263,7 +3266,7 @@
       <c r="P2" s="20"/>
       <c r="Q2" s="20"/>
     </row>
-    <row r="3" ht="102.95" customHeight="1">
+    <row r="3" ht="154.07" customHeight="true">
       <c r="A3" s="0"/>
       <c r="B3" s="21" t="inlineStr">
         <is>
@@ -3373,7 +3376,7 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="102.95" customHeight="1">
+    <row r="4" ht="154.07" customHeight="true">
       <c r="A4" s="0"/>
       <c r="B4" s="21" t="inlineStr">
         <is>
@@ -3462,7 +3465,7 @@
       </c>
       <c r="Q4" s="25"/>
     </row>
-    <row r="5" ht="102.95" customHeight="1">
+    <row r="5" ht="154.07" customHeight="true">
       <c r="A5" s="0"/>
       <c r="B5" s="21" t="inlineStr">
         <is>
@@ -3571,7 +3574,7 @@
       </c>
       <c r="Q5" s="25"/>
     </row>
-    <row r="6" ht="102.95" customHeight="1">
+    <row r="6" ht="154.07" customHeight="true">
       <c r="A6" s="0"/>
       <c r="B6" s="21" t="inlineStr">
         <is>
@@ -3677,7 +3680,7 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="102.95" customHeight="1">
+    <row r="7" ht="154.07" customHeight="true">
       <c r="A7" s="0"/>
       <c r="B7" s="21" t="inlineStr">
         <is>
@@ -3790,7 +3793,7 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="102.95" customHeight="1">
+    <row r="8" ht="154.07" customHeight="true">
       <c r="A8" s="0"/>
       <c r="B8" s="21" t="inlineStr">
         <is>
@@ -3898,7 +3901,7 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="102.95" customHeight="1">
+    <row r="9" ht="154.07" customHeight="true">
       <c r="A9" s="0"/>
       <c r="B9" s="23" t="inlineStr">
         <is>
@@ -4014,7 +4017,7 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="102.95" customHeight="1">
+    <row r="10" ht="154.07" customHeight="true">
       <c r="A10" s="0"/>
       <c r="B10" s="23" t="inlineStr">
         <is>
@@ -4122,6 +4125,6 @@
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" scale="76"/>
+  <pageSetup paperSize="9" orientation="portrait" scale="58"/>
 </worksheet>
 </file>
--- a/sheets/민요/검수/창부타령 1.xlsx
+++ b/sheets/민요/검수/창부타령 1.xlsx
@@ -3222,28 +3222,28 @@
   </sheetPr>
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
-    <col min="2" max="2" width="12" customWidth="1"/>
+    <col min="2" max="2" width="10.71" customWidth="1"/>
     <col min="3" max="3" width="6" customWidth="1"/>
-    <col min="4" max="4" width="12" customWidth="1"/>
+    <col min="4" max="4" width="10.71" customWidth="1"/>
     <col min="5" max="5" width="6" customWidth="1"/>
-    <col min="6" max="6" width="12" customWidth="1"/>
+    <col min="6" max="6" width="10.71" customWidth="1"/>
     <col min="7" max="7" width="6" customWidth="1"/>
-    <col min="8" max="8" width="12" customWidth="1"/>
+    <col min="8" max="8" width="10.71" customWidth="1"/>
     <col min="9" max="9" width="6" customWidth="1"/>
-    <col min="10" max="10" width="12" customWidth="1"/>
+    <col min="10" max="10" width="10.71" customWidth="1"/>
     <col min="11" max="11" width="6" customWidth="1"/>
-    <col min="12" max="12" width="12" customWidth="1"/>
+    <col min="12" max="12" width="10.71" customWidth="1"/>
     <col min="13" max="13" width="6" customWidth="1"/>
-    <col min="14" max="14" width="12" customWidth="1"/>
+    <col min="14" max="14" width="10.71" customWidth="1"/>
     <col min="15" max="15" width="6" customWidth="1"/>
-    <col min="16" max="16" width="12" customWidth="1"/>
+    <col min="16" max="16" width="10.71" customWidth="1"/>
     <col min="17" max="17" width="6" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="6.0" customHeight="true">
       <c r="A1" s="0"/>
     </row>
-    <row r="2" ht="68.97" customHeight="true">
+    <row r="2" ht="64.52" customHeight="true">
       <c r="A2" s="0"/>
       <c r="B2" s="20" t="inlineStr">
         <is>
@@ -3266,7 +3266,7 @@
       <c r="P2" s="20"/>
       <c r="Q2" s="20"/>
     </row>
-    <row r="3" ht="154.07" customHeight="true">
+    <row r="3" ht="144.08" customHeight="true">
       <c r="A3" s="0"/>
       <c r="B3" s="21" t="inlineStr">
         <is>
@@ -3376,7 +3376,7 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="154.07" customHeight="true">
+    <row r="4" ht="144.08" customHeight="true">
       <c r="A4" s="0"/>
       <c r="B4" s="21" t="inlineStr">
         <is>
@@ -3465,7 +3465,7 @@
       </c>
       <c r="Q4" s="25"/>
     </row>
-    <row r="5" ht="154.07" customHeight="true">
+    <row r="5" ht="144.08" customHeight="true">
       <c r="A5" s="0"/>
       <c r="B5" s="21" t="inlineStr">
         <is>
@@ -3574,7 +3574,7 @@
       </c>
       <c r="Q5" s="25"/>
     </row>
-    <row r="6" ht="154.07" customHeight="true">
+    <row r="6" ht="144.08" customHeight="true">
       <c r="A6" s="0"/>
       <c r="B6" s="21" t="inlineStr">
         <is>
@@ -3680,7 +3680,7 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="154.07" customHeight="true">
+    <row r="7" ht="144.08" customHeight="true">
       <c r="A7" s="0"/>
       <c r="B7" s="21" t="inlineStr">
         <is>
@@ -3793,7 +3793,7 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="154.07" customHeight="true">
+    <row r="8" ht="144.08" customHeight="true">
       <c r="A8" s="0"/>
       <c r="B8" s="21" t="inlineStr">
         <is>
@@ -3901,7 +3901,7 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="154.07" customHeight="true">
+    <row r="9" ht="144.08" customHeight="true">
       <c r="A9" s="0"/>
       <c r="B9" s="23" t="inlineStr">
         <is>
@@ -4017,7 +4017,7 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="154.07" customHeight="true">
+    <row r="10" ht="144.08" customHeight="true">
       <c r="A10" s="0"/>
       <c r="B10" s="23" t="inlineStr">
         <is>
@@ -4125,6 +4125,6 @@
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" scale="58"/>
+  <pageSetup paperSize="9" orientation="portrait" scale="62"/>
 </worksheet>
 </file>